--- a/release_1_0_0/data/files/input/v1_hotel_params.xlsx
+++ b/release_1_0_0/data/files/input/v1_hotel_params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,11 @@
           <t>n_mois</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>partenaire</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -581,6 +586,11 @@
       <c r="S2" t="n">
         <v>30</v>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Adixon</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -590,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SIMPLY</t>
+          <t>CONNECTED</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -649,12 +659,17 @@
       </c>
       <c r="S3" t="n">
         <v>19</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Selfly</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H6188</t>
+          <t>HB5I0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -664,135 +679,145 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MER BOUL</t>
+          <t>NOV MEG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mercure Paris Boulogne</t>
+          <t>Novotel Megève Mont-Blanc</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MERCURE</t>
+          <t>NOVOTEL</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>191</v>
+        <v>572</v>
       </c>
       <c r="G4" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>8505.23</v>
+        <v>18841.68</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.5663</v>
       </c>
       <c r="M4" t="n">
-        <v>1125.05</v>
+        <v>1585.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1125.05</v>
+        <v>897.67</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>687.39</v>
       </c>
       <c r="P4" t="n">
-        <v>101.33</v>
+        <v>123.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>353.4</v>
+        <v>223.33</v>
       </c>
       <c r="R4" t="n">
-        <v>322.83</v>
+        <v>128.4</v>
       </c>
       <c r="S4" t="n">
-        <v>21</v>
+        <v>26</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Adixon</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HB5I0</t>
+          <t>H0373</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LIBERTY</t>
+          <t>CONNECTED</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NOV MEG</t>
+          <t>MER MONT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Novotel Megève Mont-Blanc</t>
+          <t>Mercure Paris Montmartre Sacré-Cœur</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NOVOTEL</t>
+          <t>MERCURE</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>572</v>
+        <v>305</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>18841.68</v>
+        <v>14139.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5663</v>
+        <v>0.9594</v>
       </c>
       <c r="M5" t="n">
-        <v>1585.06</v>
+        <v>4125.77</v>
       </c>
       <c r="N5" t="n">
-        <v>897.67</v>
+        <v>3958.4</v>
       </c>
       <c r="O5" t="n">
-        <v>687.39</v>
+        <v>167.37</v>
       </c>
       <c r="P5" t="n">
-        <v>123.75</v>
+        <v>21.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>223.33</v>
+        <v>564.4299999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>128.4</v>
+        <v>307.8</v>
       </c>
       <c r="S5" t="n">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Selfly</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H0373</t>
+          <t>H3546</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -802,129 +827,65 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MER MONT</t>
+          <t>NOV TE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mercure Paris Montmartre Sacré-Cœur</t>
+          <t>Novotel Paris Centre Tour Eiffel</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MERCURE</t>
+          <t>NOVOTEL</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>305</v>
+        <v>764</v>
       </c>
       <c r="G6" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>14139.8</v>
+        <v>33554.88</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9594</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>4125.77</v>
+        <v>17839.96</v>
       </c>
       <c r="N6" t="n">
-        <v>3958.4</v>
+        <v>13225.77</v>
       </c>
       <c r="O6" t="n">
-        <v>167.37</v>
+        <v>4614.2</v>
       </c>
       <c r="P6" t="n">
-        <v>21.29</v>
+        <v>1396.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>564.4299999999999</v>
+        <v>3772.78</v>
       </c>
       <c r="R6" t="n">
-        <v>307.8</v>
+        <v>1354.7</v>
       </c>
       <c r="S6" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>H3546</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CONNECTED</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>NOV TE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Novotel Paris Centre Tour Eiffel</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>NOVOTEL</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>764</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>33554.88</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.7413999999999999</v>
-      </c>
-      <c r="M7" t="n">
-        <v>17839.96</v>
-      </c>
-      <c r="N7" t="n">
-        <v>13225.77</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4614.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1396.28</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3772.78</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1354.7</v>
-      </c>
-      <c r="S7" t="n">
         <v>23</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Digitizme</t>
+        </is>
       </c>
     </row>
   </sheetData>
